--- a/public/plantillas/plantilla-shalom-masivo.xlsx
+++ b/public/plantillas/plantilla-shalom-masivo.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="2197">
   <si>
     <t>DESTINATARIO (DOC)</t>
   </si>
@@ -6520,6 +6520,9 @@
     <t>CUSCO PARQUE INDUSTRIAL</t>
   </si>
   <si>
+    <t>EL RETAMAL</t>
+  </si>
+  <si>
     <t>HUARAZ CO</t>
   </si>
   <si>
@@ -6533,6 +6536,9 @@
   </si>
   <si>
     <t>JAEN CO</t>
+  </si>
+  <si>
+    <t>JR MAYRO</t>
   </si>
   <si>
     <t>JR. MAMA OCLLO</t>
@@ -22024,304 +22030,304 @@
       <formula1>"SOBRE,PAQUETE XXS,PAQUETE XS,PAQUETE S,PAQUETE M,PAQUETE L"</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F2">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G2">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F3">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G3">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F4">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G4">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F5">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G5">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F6">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G6">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F7">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G7">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F8">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G8">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F9">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G9">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F10">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G10">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F11">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G11">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F12">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G12">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F13">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G13">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F14">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G14">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F15">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G15">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F16">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G16">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F17">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G17">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F18">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G18">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F19">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G19">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F20">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G20">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F21">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G21">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F22">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G22">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F23">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G23">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F24">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G24">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F25">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G25">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F26">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G26">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F27">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G27">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F28">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G28">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F29">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G29">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F30">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G30">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F31">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G31">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F32">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G32">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F33">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G33">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F34">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G34">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F35">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G35">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F36">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G36">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F37">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G37">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F38">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G38">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F39">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G39">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F40">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G40">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F41">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G41">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F42">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G42">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F43">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G43">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F44">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G44">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F45">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G45">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F46">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G46">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F47">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G47">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F48">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G48">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F49">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G49">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F50">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G50">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="F51">
-      <formula1>'Hoja2'!B1:B507</formula1>
+      <formula1>'Hoja2'!B1:B509</formula1>
     </dataValidation>
     <dataValidation type="list" errorStyle="information" allowBlank="0" showDropDown="0" showInputMessage="0" showErrorMessage="0" errorTitle="Error de escritura" error="Valor fuera de lista" sqref="G51">
-      <formula1>'Hoja2'!C2:C496</formula1>
+      <formula1>'Hoja2'!C2:C498</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions gridLines="false" gridLinesSet="true"/>
@@ -39808,7 +39814,7 @@
         <v>2166</v>
       </c>
       <c r="C226" t="s">
-        <v>601</v>
+        <v>2167</v>
       </c>
       <c r="G226" t="s">
         <v>152</v>
@@ -39822,7 +39828,7 @@
         <v>589</v>
       </c>
       <c r="C227" t="s">
-        <v>239</v>
+        <v>601</v>
       </c>
       <c r="G227" t="s">
         <v>155</v>
@@ -39836,7 +39842,7 @@
         <v>224</v>
       </c>
       <c r="C228" t="s">
-        <v>604</v>
+        <v>239</v>
       </c>
       <c r="G228" t="s">
         <v>620</v>
@@ -39850,7 +39856,7 @@
         <v>591</v>
       </c>
       <c r="C229" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="G229" t="s">
         <v>516</v>
@@ -39864,7 +39870,7 @@
         <v>593</v>
       </c>
       <c r="C230" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G230" t="s">
         <v>622</v>
@@ -39878,7 +39884,7 @@
         <v>595</v>
       </c>
       <c r="C231" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="G231" t="s">
         <v>623</v>
@@ -39892,7 +39898,7 @@
         <v>597</v>
       </c>
       <c r="C232" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G232" t="s">
         <v>625</v>
@@ -39906,7 +39912,7 @@
         <v>599</v>
       </c>
       <c r="C233" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G233" t="s">
         <v>626</v>
@@ -39914,13 +39920,13 @@
     </row>
     <row r="234" spans="1:9">
       <c r="A234">
-        <v>639</v>
+        <v>716</v>
       </c>
       <c r="B234" t="s">
-        <v>601</v>
+        <v>2167</v>
       </c>
       <c r="C234" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="G234" t="s">
         <v>628</v>
@@ -39928,13 +39934,13 @@
     </row>
     <row r="235" spans="1:9">
       <c r="A235">
-        <v>75</v>
+        <v>639</v>
       </c>
       <c r="B235" t="s">
-        <v>239</v>
+        <v>601</v>
       </c>
       <c r="C235" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="G235" t="s">
         <v>629</v>
@@ -39942,13 +39948,13 @@
     </row>
     <row r="236" spans="1:9">
       <c r="A236">
-        <v>138</v>
+        <v>75</v>
       </c>
       <c r="B236" t="s">
-        <v>604</v>
+        <v>239</v>
       </c>
       <c r="C236" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G236" t="s">
         <v>630</v>
@@ -39956,13 +39962,13 @@
     </row>
     <row r="237" spans="1:9">
       <c r="A237">
-        <v>68</v>
+        <v>138</v>
       </c>
       <c r="B237" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C237" t="s">
-        <v>268</v>
+        <v>618</v>
       </c>
       <c r="G237" t="s">
         <v>158</v>
@@ -39970,13 +39976,13 @@
     </row>
     <row r="238" spans="1:9">
       <c r="A238">
-        <v>564</v>
+        <v>68</v>
       </c>
       <c r="B238" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="C238" t="s">
-        <v>619</v>
+        <v>268</v>
       </c>
       <c r="G238" t="s">
         <v>633</v>
@@ -39984,13 +39990,13 @@
     </row>
     <row r="239" spans="1:9">
       <c r="A239">
-        <v>389</v>
+        <v>564</v>
       </c>
       <c r="B239" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C239" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G239" t="s">
         <v>635</v>
@@ -39998,13 +40004,13 @@
     </row>
     <row r="240" spans="1:9">
       <c r="A240">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="B240" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C240" t="s">
-        <v>280</v>
+        <v>621</v>
       </c>
       <c r="G240" t="s">
         <v>637</v>
@@ -40012,13 +40018,13 @@
     </row>
     <row r="241" spans="1:9">
       <c r="A241">
-        <v>151</v>
+        <v>425</v>
       </c>
       <c r="B241" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C241" t="s">
-        <v>624</v>
+        <v>280</v>
       </c>
       <c r="G241" t="s">
         <v>639</v>
@@ -40026,13 +40032,13 @@
     </row>
     <row r="242" spans="1:9">
       <c r="A242">
-        <v>441</v>
+        <v>151</v>
       </c>
       <c r="B242" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="C242" t="s">
-        <v>287</v>
+        <v>624</v>
       </c>
       <c r="G242" t="s">
         <v>641</v>
@@ -40040,13 +40046,13 @@
     </row>
     <row r="243" spans="1:9">
       <c r="A243">
-        <v>118</v>
+        <v>441</v>
       </c>
       <c r="B243" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C243" t="s">
-        <v>2167</v>
+        <v>287</v>
       </c>
       <c r="G243" t="s">
         <v>643</v>
@@ -40054,13 +40060,13 @@
     </row>
     <row r="244" spans="1:9">
       <c r="A244">
-        <v>555</v>
+        <v>118</v>
       </c>
       <c r="B244" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C244" t="s">
-        <v>295</v>
+        <v>2168</v>
       </c>
       <c r="G244" t="s">
         <v>645</v>
@@ -40068,13 +40074,13 @@
     </row>
     <row r="245" spans="1:9">
       <c r="A245">
-        <v>422</v>
+        <v>555</v>
       </c>
       <c r="B245" t="s">
-        <v>268</v>
+        <v>618</v>
       </c>
       <c r="C245" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G245" t="s">
         <v>647</v>
@@ -40082,13 +40088,13 @@
     </row>
     <row r="246" spans="1:9">
       <c r="A246">
-        <v>650</v>
+        <v>422</v>
       </c>
       <c r="B246" t="s">
-        <v>619</v>
+        <v>268</v>
       </c>
       <c r="C246" t="s">
-        <v>631</v>
+        <v>300</v>
       </c>
       <c r="G246" t="s">
         <v>164</v>
@@ -40096,27 +40102,27 @@
     </row>
     <row r="247" spans="1:9">
       <c r="A247">
-        <v>181</v>
+        <v>650</v>
       </c>
       <c r="B247" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C247" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="G247" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="248" spans="1:9">
       <c r="A248">
-        <v>143</v>
+        <v>181</v>
       </c>
       <c r="B248" t="s">
-        <v>280</v>
+        <v>621</v>
       </c>
       <c r="C248" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G248" t="s">
         <v>650</v>
@@ -40124,13 +40130,13 @@
     </row>
     <row r="249" spans="1:9">
       <c r="A249">
-        <v>554</v>
+        <v>143</v>
       </c>
       <c r="B249" t="s">
-        <v>624</v>
+        <v>280</v>
       </c>
       <c r="C249" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G249" t="s">
         <v>652</v>
@@ -40138,13 +40144,13 @@
     </row>
     <row r="250" spans="1:9">
       <c r="A250">
-        <v>124</v>
+        <v>554</v>
       </c>
       <c r="B250" t="s">
-        <v>287</v>
+        <v>624</v>
       </c>
       <c r="C250" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G250" t="s">
         <v>654</v>
@@ -40152,13 +40158,13 @@
     </row>
     <row r="251" spans="1:9">
       <c r="A251">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B251" t="s">
-        <v>2167</v>
+        <v>287</v>
       </c>
       <c r="C251" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G251" t="s">
         <v>656</v>
@@ -40166,13 +40172,13 @@
     </row>
     <row r="252" spans="1:9">
       <c r="A252">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="B252" t="s">
-        <v>295</v>
+        <v>2168</v>
       </c>
       <c r="C252" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G252" t="s">
         <v>658</v>
@@ -40180,13 +40186,13 @@
     </row>
     <row r="253" spans="1:9">
       <c r="A253">
-        <v>394</v>
+        <v>183</v>
       </c>
       <c r="B253" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C253" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G253" t="s">
         <v>660</v>
@@ -40194,13 +40200,13 @@
     </row>
     <row r="254" spans="1:9">
       <c r="A254">
-        <v>620</v>
+        <v>394</v>
       </c>
       <c r="B254" t="s">
-        <v>631</v>
+        <v>300</v>
       </c>
       <c r="C254" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G254" t="s">
         <v>662</v>
@@ -40208,13 +40214,13 @@
     </row>
     <row r="255" spans="1:9">
       <c r="A255">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="B255" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C255" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G255" t="s">
         <v>664</v>
@@ -40222,13 +40228,13 @@
     </row>
     <row r="256" spans="1:9">
       <c r="A256">
-        <v>216</v>
+        <v>636</v>
       </c>
       <c r="B256" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C256" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="G256" t="s">
         <v>167</v>
@@ -40236,13 +40242,13 @@
     </row>
     <row r="257" spans="1:9">
       <c r="A257">
-        <v>60</v>
+        <v>216</v>
       </c>
       <c r="B257" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C257" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G257" t="s">
         <v>667</v>
@@ -40250,13 +40256,13 @@
     </row>
     <row r="258" spans="1:9">
       <c r="A258">
-        <v>132</v>
+        <v>60</v>
       </c>
       <c r="B258" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C258" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G258" t="s">
         <v>668</v>
@@ -40264,13 +40270,13 @@
     </row>
     <row r="259" spans="1:9">
       <c r="A259">
-        <v>558</v>
+        <v>132</v>
       </c>
       <c r="B259" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C259" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G259" t="s">
         <v>670</v>
@@ -40278,13 +40284,13 @@
     </row>
     <row r="260" spans="1:9">
       <c r="A260">
-        <v>405</v>
+        <v>558</v>
       </c>
       <c r="B260" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C260" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G260" t="s">
         <v>671</v>
@@ -40292,13 +40298,13 @@
     </row>
     <row r="261" spans="1:9">
       <c r="A261">
-        <v>8</v>
+        <v>405</v>
       </c>
       <c r="B261" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C261" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G261" t="s">
         <v>673</v>
@@ -40306,13 +40312,13 @@
     </row>
     <row r="262" spans="1:9">
       <c r="A262">
-        <v>402</v>
+        <v>8</v>
       </c>
       <c r="B262" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C262" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G262" t="s">
         <v>532</v>
@@ -40320,13 +40326,13 @@
     </row>
     <row r="263" spans="1:9">
       <c r="A263">
-        <v>608</v>
+        <v>402</v>
       </c>
       <c r="B263" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C263" t="s">
-        <v>2169</v>
+        <v>661</v>
       </c>
       <c r="G263" t="s">
         <v>676</v>
@@ -40334,10 +40340,10 @@
     </row>
     <row r="264" spans="1:9">
       <c r="A264">
-        <v>417</v>
+        <v>608</v>
       </c>
       <c r="B264" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C264" t="s">
         <v>2170</v>
@@ -40348,13 +40354,13 @@
     </row>
     <row r="265" spans="1:9">
       <c r="A265">
-        <v>470</v>
+        <v>417</v>
       </c>
       <c r="B265" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C265" t="s">
-        <v>666</v>
+        <v>2171</v>
       </c>
       <c r="G265" t="s">
         <v>680</v>
@@ -40362,13 +40368,13 @@
     </row>
     <row r="266" spans="1:9">
       <c r="A266">
-        <v>368</v>
+        <v>470</v>
       </c>
       <c r="B266" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C266" t="s">
-        <v>2171</v>
+        <v>666</v>
       </c>
       <c r="G266" t="s">
         <v>682</v>
@@ -40376,13 +40382,13 @@
     </row>
     <row r="267" spans="1:9">
       <c r="A267">
-        <v>20</v>
+        <v>368</v>
       </c>
       <c r="B267" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C267" t="s">
-        <v>319</v>
+        <v>2172</v>
       </c>
       <c r="G267" t="s">
         <v>684</v>
@@ -40390,13 +40396,13 @@
     </row>
     <row r="268" spans="1:9">
       <c r="A268">
-        <v>515</v>
+        <v>20</v>
       </c>
       <c r="B268" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C268" t="s">
-        <v>672</v>
+        <v>319</v>
       </c>
       <c r="G268" t="s">
         <v>686</v>
@@ -40404,13 +40410,13 @@
     </row>
     <row r="269" spans="1:9">
       <c r="A269">
-        <v>308</v>
+        <v>515</v>
       </c>
       <c r="B269" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C269" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G269" t="s">
         <v>688</v>
@@ -40418,13 +40424,13 @@
     </row>
     <row r="270" spans="1:9">
       <c r="A270">
-        <v>624</v>
+        <v>308</v>
       </c>
       <c r="B270" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C270" t="s">
-        <v>1258</v>
+        <v>674</v>
       </c>
       <c r="G270" t="s">
         <v>690</v>
@@ -40432,13 +40438,13 @@
     </row>
     <row r="271" spans="1:9">
       <c r="A271">
-        <v>460</v>
+        <v>624</v>
       </c>
       <c r="B271" t="s">
-        <v>2169</v>
+        <v>661</v>
       </c>
       <c r="C271" t="s">
-        <v>675</v>
+        <v>1258</v>
       </c>
       <c r="G271" t="s">
         <v>535</v>
@@ -40446,13 +40452,13 @@
     </row>
     <row r="272" spans="1:9">
       <c r="A272">
-        <v>52</v>
+        <v>460</v>
       </c>
       <c r="B272" t="s">
         <v>2170</v>
       </c>
       <c r="C272" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G272" t="s">
         <v>693</v>
@@ -40460,13 +40466,13 @@
     </row>
     <row r="273" spans="1:9">
       <c r="A273">
-        <v>556</v>
+        <v>52</v>
       </c>
       <c r="B273" t="s">
-        <v>666</v>
+        <v>2171</v>
       </c>
       <c r="C273" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="G273" t="s">
         <v>695</v>
@@ -40474,13 +40480,13 @@
     </row>
     <row r="274" spans="1:9">
       <c r="A274">
-        <v>28</v>
+        <v>556</v>
       </c>
       <c r="B274" t="s">
-        <v>2171</v>
+        <v>666</v>
       </c>
       <c r="C274" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G274" t="s">
         <v>537</v>
@@ -40488,10 +40494,10 @@
     </row>
     <row r="275" spans="1:9">
       <c r="A275">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B275" t="s">
-        <v>319</v>
+        <v>2172</v>
       </c>
       <c r="C275" t="s">
         <v>683</v>
@@ -40502,10 +40508,10 @@
     </row>
     <row r="276" spans="1:9">
       <c r="A276">
-        <v>549</v>
+        <v>13</v>
       </c>
       <c r="B276" t="s">
-        <v>672</v>
+        <v>319</v>
       </c>
       <c r="C276" t="s">
         <v>685</v>
@@ -40516,10 +40522,10 @@
     </row>
     <row r="277" spans="1:9">
       <c r="A277">
-        <v>374</v>
+        <v>549</v>
       </c>
       <c r="B277" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C277" t="s">
         <v>687</v>
@@ -40530,10 +40536,10 @@
     </row>
     <row r="278" spans="1:9">
       <c r="A278">
-        <v>438</v>
+        <v>374</v>
       </c>
       <c r="B278" t="s">
-        <v>1258</v>
+        <v>674</v>
       </c>
       <c r="C278" t="s">
         <v>689</v>
@@ -40544,13 +40550,13 @@
     </row>
     <row r="279" spans="1:9">
       <c r="A279">
-        <v>473</v>
+        <v>438</v>
       </c>
       <c r="B279" t="s">
-        <v>675</v>
+        <v>1258</v>
       </c>
       <c r="C279" t="s">
-        <v>691</v>
+        <v>2173</v>
       </c>
       <c r="G279" t="s">
         <v>706</v>
@@ -40558,13 +40564,13 @@
     </row>
     <row r="280" spans="1:9">
       <c r="A280">
-        <v>655</v>
+        <v>473</v>
       </c>
       <c r="B280" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C280" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G280" t="s">
         <v>708</v>
@@ -40572,13 +40578,13 @@
     </row>
     <row r="281" spans="1:9">
       <c r="A281">
-        <v>566</v>
+        <v>655</v>
       </c>
       <c r="B281" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C281" t="s">
-        <v>2172</v>
+        <v>692</v>
       </c>
       <c r="G281" t="s">
         <v>710</v>
@@ -40586,13 +40592,13 @@
     </row>
     <row r="282" spans="1:9">
       <c r="A282">
-        <v>27</v>
+        <v>566</v>
       </c>
       <c r="B282" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C282" t="s">
-        <v>696</v>
+        <v>2174</v>
       </c>
       <c r="G282" t="s">
         <v>712</v>
@@ -40606,7 +40612,7 @@
         <v>683</v>
       </c>
       <c r="C283" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G283" t="s">
         <v>715</v>
@@ -40620,7 +40626,7 @@
         <v>685</v>
       </c>
       <c r="C284" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G284" t="s">
         <v>717</v>
@@ -40634,7 +40640,7 @@
         <v>687</v>
       </c>
       <c r="C285" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="G285" t="s">
         <v>719</v>
@@ -40648,7 +40654,7 @@
         <v>689</v>
       </c>
       <c r="C286" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G286" t="s">
         <v>721</v>
@@ -40656,13 +40662,13 @@
     </row>
     <row r="287" spans="1:9">
       <c r="A287">
-        <v>574</v>
+        <v>27</v>
       </c>
       <c r="B287" t="s">
-        <v>691</v>
+        <v>2173</v>
       </c>
       <c r="C287" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="G287" t="s">
         <v>722</v>
@@ -40670,13 +40676,13 @@
     </row>
     <row r="288" spans="1:9">
       <c r="A288">
-        <v>476</v>
+        <v>574</v>
       </c>
       <c r="B288" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="C288" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="G288" t="s">
         <v>724</v>
@@ -40684,13 +40690,13 @@
     </row>
     <row r="289" spans="1:9">
       <c r="A289">
-        <v>5</v>
+        <v>476</v>
       </c>
       <c r="B289" t="s">
-        <v>713</v>
+        <v>692</v>
       </c>
       <c r="C289" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="G289" t="s">
         <v>725</v>
@@ -40698,13 +40704,13 @@
     </row>
     <row r="290" spans="1:9">
       <c r="A290">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="B290" t="s">
-        <v>2172</v>
+        <v>713</v>
       </c>
       <c r="C290" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="G290" t="s">
         <v>173</v>
@@ -40712,13 +40718,13 @@
     </row>
     <row r="291" spans="1:9">
       <c r="A291">
-        <v>509</v>
+        <v>29</v>
       </c>
       <c r="B291" t="s">
-        <v>696</v>
+        <v>2174</v>
       </c>
       <c r="C291" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="G291" t="s">
         <v>728</v>
@@ -40726,13 +40732,13 @@
     </row>
     <row r="292" spans="1:9">
       <c r="A292">
-        <v>43</v>
+        <v>509</v>
       </c>
       <c r="B292" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C292" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G292" t="s">
         <v>730</v>
@@ -40740,13 +40746,13 @@
     </row>
     <row r="293" spans="1:9">
       <c r="A293">
-        <v>501</v>
+        <v>43</v>
       </c>
       <c r="B293" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C293" t="s">
-        <v>336</v>
+        <v>720</v>
       </c>
       <c r="G293" t="s">
         <v>732</v>
@@ -40754,13 +40760,13 @@
     </row>
     <row r="294" spans="1:9">
       <c r="A294">
-        <v>644</v>
+        <v>501</v>
       </c>
       <c r="B294" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C294" t="s">
-        <v>723</v>
+        <v>336</v>
       </c>
       <c r="G294" t="s">
         <v>734</v>
@@ -40768,13 +40774,13 @@
     </row>
     <row r="295" spans="1:9">
       <c r="A295">
-        <v>232</v>
+        <v>644</v>
       </c>
       <c r="B295" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C295" t="s">
-        <v>339</v>
+        <v>723</v>
       </c>
       <c r="G295" t="s">
         <v>736</v>
@@ -40782,13 +40788,13 @@
     </row>
     <row r="296" spans="1:9">
       <c r="A296">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="B296" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="C296" t="s">
-        <v>726</v>
+        <v>339</v>
       </c>
       <c r="G296" t="s">
         <v>738</v>
@@ -40796,13 +40802,13 @@
     </row>
     <row r="297" spans="1:9">
       <c r="A297">
-        <v>552</v>
+        <v>172</v>
       </c>
       <c r="B297" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C297" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="G297" t="s">
         <v>740</v>
@@ -40810,13 +40816,13 @@
     </row>
     <row r="298" spans="1:9">
       <c r="A298">
-        <v>90</v>
+        <v>552</v>
       </c>
       <c r="B298" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C298" t="s">
-        <v>2173</v>
+        <v>727</v>
       </c>
       <c r="G298" t="s">
         <v>176</v>
@@ -40824,13 +40830,13 @@
     </row>
     <row r="299" spans="1:9">
       <c r="A299">
-        <v>166</v>
+        <v>90</v>
       </c>
       <c r="B299" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C299" t="s">
-        <v>729</v>
+        <v>2175</v>
       </c>
       <c r="G299" t="s">
         <v>743</v>
@@ -40838,13 +40844,13 @@
     </row>
     <row r="300" spans="1:9">
       <c r="A300">
-        <v>242</v>
+        <v>166</v>
       </c>
       <c r="B300" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C300" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G300" t="s">
         <v>745</v>
@@ -40852,13 +40858,13 @@
     </row>
     <row r="301" spans="1:9">
       <c r="A301">
-        <v>403</v>
+        <v>242</v>
       </c>
       <c r="B301" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C301" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G301" t="s">
         <v>746</v>
@@ -40866,13 +40872,13 @@
     </row>
     <row r="302" spans="1:9">
       <c r="A302">
-        <v>100</v>
+        <v>403</v>
       </c>
       <c r="B302" t="s">
-        <v>336</v>
+        <v>720</v>
       </c>
       <c r="C302" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G302" t="s">
         <v>748</v>
@@ -40880,13 +40886,13 @@
     </row>
     <row r="303" spans="1:9">
       <c r="A303">
-        <v>472</v>
+        <v>100</v>
       </c>
       <c r="B303" t="s">
-        <v>723</v>
+        <v>336</v>
       </c>
       <c r="C303" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G303" t="s">
         <v>750</v>
@@ -40894,13 +40900,13 @@
     </row>
     <row r="304" spans="1:9">
       <c r="A304">
-        <v>318</v>
+        <v>472</v>
       </c>
       <c r="B304" t="s">
-        <v>339</v>
+        <v>723</v>
       </c>
       <c r="C304" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G304" t="s">
         <v>752</v>
@@ -40908,13 +40914,13 @@
     </row>
     <row r="305" spans="1:9">
       <c r="A305">
-        <v>618</v>
+        <v>318</v>
       </c>
       <c r="B305" t="s">
-        <v>726</v>
+        <v>339</v>
       </c>
       <c r="C305" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G305" t="s">
         <v>547</v>
@@ -40922,13 +40928,13 @@
     </row>
     <row r="306" spans="1:9">
       <c r="A306">
-        <v>171</v>
+        <v>618</v>
       </c>
       <c r="B306" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C306" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G306" t="s">
         <v>755</v>
@@ -40936,13 +40942,13 @@
     </row>
     <row r="307" spans="1:9">
       <c r="A307">
-        <v>661</v>
+        <v>171</v>
       </c>
       <c r="B307" t="s">
-        <v>2173</v>
+        <v>727</v>
       </c>
       <c r="C307" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G307" t="s">
         <v>757</v>
@@ -40950,13 +40956,13 @@
     </row>
     <row r="308" spans="1:9">
       <c r="A308">
-        <v>45</v>
+        <v>661</v>
       </c>
       <c r="B308" t="s">
-        <v>729</v>
+        <v>2175</v>
       </c>
       <c r="C308" t="s">
-        <v>359</v>
+        <v>744</v>
       </c>
       <c r="G308" t="s">
         <v>759</v>
@@ -40964,13 +40970,13 @@
     </row>
     <row r="309" spans="1:9">
       <c r="A309">
-        <v>327</v>
+        <v>45</v>
       </c>
       <c r="B309" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C309" t="s">
-        <v>747</v>
+        <v>359</v>
       </c>
       <c r="G309" t="s">
         <v>761</v>
@@ -40978,13 +40984,13 @@
     </row>
     <row r="310" spans="1:9">
       <c r="A310">
-        <v>391</v>
+        <v>327</v>
       </c>
       <c r="B310" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C310" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="G310" t="s">
         <v>763</v>
@@ -40992,13 +40998,13 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="B311" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C311" t="s">
-        <v>2174</v>
+        <v>751</v>
       </c>
       <c r="G311" t="s">
         <v>765</v>
@@ -41006,13 +41012,13 @@
     </row>
     <row r="312" spans="1:9">
       <c r="A312">
-        <v>449</v>
+        <v>399</v>
       </c>
       <c r="B312" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C312" t="s">
-        <v>753</v>
+        <v>2176</v>
       </c>
       <c r="G312" t="s">
         <v>767</v>
@@ -41020,13 +41026,13 @@
     </row>
     <row r="313" spans="1:9">
       <c r="A313">
-        <v>426</v>
+        <v>449</v>
       </c>
       <c r="B313" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C313" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="G313" t="s">
         <v>768</v>
@@ -41034,13 +41040,13 @@
     </row>
     <row r="314" spans="1:9">
       <c r="A314">
-        <v>135</v>
+        <v>426</v>
       </c>
       <c r="B314" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C314" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G314" t="s">
         <v>552</v>
@@ -41048,13 +41054,13 @@
     </row>
     <row r="315" spans="1:9">
       <c r="A315">
-        <v>411</v>
+        <v>135</v>
       </c>
       <c r="B315" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C315" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G315" t="s">
         <v>182</v>
@@ -41062,13 +41068,13 @@
     </row>
     <row r="316" spans="1:9">
       <c r="A316">
-        <v>217</v>
+        <v>411</v>
       </c>
       <c r="B316" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C316" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G316" t="s">
         <v>772</v>
@@ -41076,13 +41082,13 @@
     </row>
     <row r="317" spans="1:9">
       <c r="A317">
-        <v>468</v>
+        <v>217</v>
       </c>
       <c r="B317" t="s">
-        <v>359</v>
+        <v>744</v>
       </c>
       <c r="C317" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="G317" t="s">
         <v>774</v>
@@ -41090,13 +41096,13 @@
     </row>
     <row r="318" spans="1:9">
       <c r="A318">
-        <v>186</v>
+        <v>468</v>
       </c>
       <c r="B318" t="s">
-        <v>747</v>
+        <v>359</v>
       </c>
       <c r="C318" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G318" t="s">
         <v>776</v>
@@ -41104,13 +41110,13 @@
     </row>
     <row r="319" spans="1:9">
       <c r="A319">
-        <v>156</v>
+        <v>186</v>
       </c>
       <c r="B319" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C319" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G319" t="s">
         <v>778</v>
@@ -41118,13 +41124,13 @@
     </row>
     <row r="320" spans="1:9">
       <c r="A320">
-        <v>677</v>
+        <v>156</v>
       </c>
       <c r="B320" t="s">
-        <v>2174</v>
+        <v>751</v>
       </c>
       <c r="C320" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="G320" t="s">
         <v>780</v>
@@ -41132,13 +41138,13 @@
     </row>
     <row r="321" spans="1:9">
       <c r="A321">
-        <v>392</v>
+        <v>677</v>
       </c>
       <c r="B321" t="s">
-        <v>753</v>
+        <v>2176</v>
       </c>
       <c r="C321" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G321" t="s">
         <v>782</v>
@@ -41146,13 +41152,13 @@
     </row>
     <row r="322" spans="1:9">
       <c r="A322">
-        <v>220</v>
+        <v>392</v>
       </c>
       <c r="B322" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C322" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="G322" t="s">
         <v>784</v>
@@ -41160,13 +41166,13 @@
     </row>
     <row r="323" spans="1:9">
       <c r="A323">
-        <v>609</v>
+        <v>220</v>
       </c>
       <c r="B323" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C323" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G323" t="s">
         <v>786</v>
@@ -41174,13 +41180,13 @@
     </row>
     <row r="324" spans="1:9">
       <c r="A324">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B324" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C324" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G324" t="s">
         <v>788</v>
@@ -41188,13 +41194,13 @@
     </row>
     <row r="325" spans="1:9">
       <c r="A325">
-        <v>580</v>
+        <v>611</v>
       </c>
       <c r="B325" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C325" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G325" t="s">
         <v>789</v>
@@ -41202,13 +41208,13 @@
     </row>
     <row r="326" spans="1:9">
       <c r="A326">
-        <v>152</v>
+        <v>580</v>
       </c>
       <c r="B326" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C326" t="s">
-        <v>2175</v>
+        <v>777</v>
       </c>
       <c r="G326" t="s">
         <v>791</v>
@@ -41216,13 +41222,13 @@
     </row>
     <row r="327" spans="1:9">
       <c r="A327">
-        <v>246</v>
+        <v>152</v>
       </c>
       <c r="B327" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C327" t="s">
-        <v>779</v>
+        <v>2177</v>
       </c>
       <c r="G327" t="s">
         <v>793</v>
@@ -41230,13 +41236,13 @@
     </row>
     <row r="328" spans="1:9">
       <c r="A328">
-        <v>153</v>
+        <v>246</v>
       </c>
       <c r="B328" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C328" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G328" t="s">
         <v>795</v>
@@ -41244,13 +41250,13 @@
     </row>
     <row r="329" spans="1:9">
       <c r="A329">
-        <v>648</v>
+        <v>153</v>
       </c>
       <c r="B329" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C329" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G329" t="s">
         <v>797</v>
@@ -41258,13 +41264,13 @@
     </row>
     <row r="330" spans="1:9">
       <c r="A330">
-        <v>455</v>
+        <v>648</v>
       </c>
       <c r="B330" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C330" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G330" t="s">
         <v>799</v>
@@ -41272,13 +41278,13 @@
     </row>
     <row r="331" spans="1:9">
       <c r="A331">
-        <v>299</v>
+        <v>455</v>
       </c>
       <c r="B331" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C331" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="G331" t="s">
         <v>801</v>
@@ -41286,13 +41292,13 @@
     </row>
     <row r="332" spans="1:9">
       <c r="A332">
-        <v>450</v>
+        <v>299</v>
       </c>
       <c r="B332" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C332" t="s">
-        <v>389</v>
+        <v>787</v>
       </c>
       <c r="G332" t="s">
         <v>803</v>
@@ -41300,13 +41306,13 @@
     </row>
     <row r="333" spans="1:9">
       <c r="A333">
-        <v>532</v>
+        <v>450</v>
       </c>
       <c r="B333" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C333" t="s">
-        <v>790</v>
+        <v>389</v>
       </c>
       <c r="G333" t="s">
         <v>805</v>
@@ -41314,13 +41320,13 @@
     </row>
     <row r="334" spans="1:9">
       <c r="A334">
-        <v>638</v>
+        <v>532</v>
       </c>
       <c r="B334" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C334" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="G334" t="s">
         <v>806</v>
@@ -41328,13 +41334,13 @@
     </row>
     <row r="335" spans="1:9">
       <c r="A335">
-        <v>162</v>
+        <v>638</v>
       </c>
       <c r="B335" t="s">
-        <v>2175</v>
+        <v>777</v>
       </c>
       <c r="C335" t="s">
-        <v>2176</v>
+        <v>792</v>
       </c>
       <c r="G335" t="s">
         <v>554</v>
@@ -41342,13 +41348,13 @@
     </row>
     <row r="336" spans="1:9">
       <c r="A336">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B336" t="s">
-        <v>779</v>
+        <v>2177</v>
       </c>
       <c r="C336" t="s">
-        <v>794</v>
+        <v>2178</v>
       </c>
       <c r="G336" t="s">
         <v>809</v>
@@ -41356,13 +41362,13 @@
     </row>
     <row r="337" spans="1:9">
       <c r="A337">
-        <v>444</v>
+        <v>158</v>
       </c>
       <c r="B337" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C337" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="G337" t="s">
         <v>811</v>
@@ -41370,13 +41376,13 @@
     </row>
     <row r="338" spans="1:9">
       <c r="A338">
-        <v>282</v>
+        <v>444</v>
       </c>
       <c r="B338" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C338" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G338" t="s">
         <v>813</v>
@@ -41384,13 +41390,13 @@
     </row>
     <row r="339" spans="1:9">
       <c r="A339">
-        <v>600</v>
+        <v>282</v>
       </c>
       <c r="B339" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C339" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G339" t="s">
         <v>815</v>
@@ -41398,13 +41404,13 @@
     </row>
     <row r="340" spans="1:9">
       <c r="A340">
-        <v>494</v>
+        <v>600</v>
       </c>
       <c r="B340" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C340" t="s">
-        <v>1504</v>
+        <v>800</v>
       </c>
       <c r="G340" t="s">
         <v>817</v>
@@ -41412,13 +41418,13 @@
     </row>
     <row r="341" spans="1:9">
       <c r="A341">
-        <v>103</v>
+        <v>494</v>
       </c>
       <c r="B341" t="s">
-        <v>389</v>
+        <v>787</v>
       </c>
       <c r="C341" t="s">
-        <v>802</v>
+        <v>1504</v>
       </c>
       <c r="G341" t="s">
         <v>557</v>
@@ -41426,13 +41432,13 @@
     </row>
     <row r="342" spans="1:9">
       <c r="A342">
-        <v>160</v>
+        <v>103</v>
       </c>
       <c r="B342" t="s">
-        <v>790</v>
+        <v>389</v>
       </c>
       <c r="C342" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="G342" t="s">
         <v>185</v>
@@ -41440,13 +41446,13 @@
     </row>
     <row r="343" spans="1:9">
       <c r="A343">
-        <v>640</v>
+        <v>160</v>
       </c>
       <c r="B343" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C343" t="s">
-        <v>400</v>
+        <v>804</v>
       </c>
       <c r="G343" t="s">
         <v>820</v>
@@ -41454,13 +41460,13 @@
     </row>
     <row r="344" spans="1:9">
       <c r="A344">
-        <v>14</v>
+        <v>640</v>
       </c>
       <c r="B344" t="s">
-        <v>2176</v>
+        <v>792</v>
       </c>
       <c r="C344" t="s">
-        <v>807</v>
+        <v>400</v>
       </c>
       <c r="G344" t="s">
         <v>188</v>
@@ -41468,13 +41474,13 @@
     </row>
     <row r="345" spans="1:9">
       <c r="A345">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="B345" t="s">
-        <v>794</v>
+        <v>2178</v>
       </c>
       <c r="C345" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="G345" t="s">
         <v>823</v>
@@ -41482,13 +41488,13 @@
     </row>
     <row r="346" spans="1:9">
       <c r="A346">
-        <v>627</v>
+        <v>32</v>
       </c>
       <c r="B346" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C346" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="G346" t="s">
         <v>825</v>
@@ -41496,13 +41502,13 @@
     </row>
     <row r="347" spans="1:9">
       <c r="A347">
-        <v>584</v>
+        <v>627</v>
       </c>
       <c r="B347" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C347" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="G347" t="s">
         <v>567</v>
@@ -41510,13 +41516,13 @@
     </row>
     <row r="348" spans="1:9">
       <c r="A348">
-        <v>122</v>
+        <v>584</v>
       </c>
       <c r="B348" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C348" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="G348" t="s">
         <v>828</v>
@@ -41524,13 +41530,13 @@
     </row>
     <row r="349" spans="1:9">
       <c r="A349">
-        <v>680</v>
+        <v>122</v>
       </c>
       <c r="B349" t="s">
-        <v>1504</v>
+        <v>800</v>
       </c>
       <c r="C349" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="G349" t="s">
         <v>829</v>
@@ -41538,13 +41544,13 @@
     </row>
     <row r="350" spans="1:9">
       <c r="A350">
-        <v>157</v>
+        <v>680</v>
       </c>
       <c r="B350" t="s">
-        <v>802</v>
+        <v>1504</v>
       </c>
       <c r="C350" t="s">
-        <v>403</v>
+        <v>818</v>
       </c>
       <c r="G350" t="s">
         <v>831</v>
@@ -41552,13 +41558,13 @@
     </row>
     <row r="351" spans="1:9">
       <c r="A351">
-        <v>597</v>
+        <v>157</v>
       </c>
       <c r="B351" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C351" t="s">
-        <v>819</v>
+        <v>403</v>
       </c>
       <c r="G351" t="s">
         <v>833</v>
@@ -41566,13 +41572,13 @@
     </row>
     <row r="352" spans="1:9">
       <c r="A352">
-        <v>117</v>
+        <v>597</v>
       </c>
       <c r="B352" t="s">
-        <v>400</v>
+        <v>804</v>
       </c>
       <c r="C352" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="G352" t="s">
         <v>193</v>
@@ -41580,13 +41586,13 @@
     </row>
     <row r="353" spans="1:9">
       <c r="A353">
-        <v>177</v>
+        <v>117</v>
       </c>
       <c r="B353" t="s">
-        <v>807</v>
+        <v>400</v>
       </c>
       <c r="C353" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G353" t="s">
         <v>836</v>
@@ -41594,13 +41600,13 @@
     </row>
     <row r="354" spans="1:9">
       <c r="A354">
-        <v>561</v>
+        <v>177</v>
       </c>
       <c r="B354" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C354" t="s">
-        <v>2177</v>
+        <v>822</v>
       </c>
       <c r="G354" t="s">
         <v>838</v>
@@ -41608,13 +41614,13 @@
     </row>
     <row r="355" spans="1:9">
       <c r="A355">
-        <v>498</v>
+        <v>561</v>
       </c>
       <c r="B355" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C355" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="G355" t="s">
         <v>840</v>
@@ -41622,13 +41628,13 @@
     </row>
     <row r="356" spans="1:9">
       <c r="A356">
-        <v>378</v>
+        <v>498</v>
       </c>
       <c r="B356" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C356" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="G356" t="s">
         <v>842</v>
@@ -41636,13 +41642,13 @@
     </row>
     <row r="357" spans="1:9">
       <c r="A357">
-        <v>633</v>
+        <v>378</v>
       </c>
       <c r="B357" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C357" t="s">
-        <v>826</v>
+        <v>2181</v>
       </c>
       <c r="G357" t="s">
         <v>844</v>
@@ -41650,13 +41656,13 @@
     </row>
     <row r="358" spans="1:9">
       <c r="A358">
-        <v>576</v>
+        <v>633</v>
       </c>
       <c r="B358" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C358" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G358" t="s">
         <v>846</v>
@@ -41664,13 +41670,13 @@
     </row>
     <row r="359" spans="1:9">
       <c r="A359">
-        <v>277</v>
+        <v>576</v>
       </c>
       <c r="B359" t="s">
-        <v>403</v>
+        <v>818</v>
       </c>
       <c r="C359" t="s">
-        <v>417</v>
+        <v>827</v>
       </c>
       <c r="G359" t="s">
         <v>196</v>
@@ -41678,13 +41684,13 @@
     </row>
     <row r="360" spans="1:9">
       <c r="A360">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="B360" t="s">
-        <v>819</v>
+        <v>403</v>
       </c>
       <c r="C360" t="s">
-        <v>830</v>
+        <v>417</v>
       </c>
       <c r="G360" t="s">
         <v>849</v>
@@ -41692,13 +41698,13 @@
     </row>
     <row r="361" spans="1:9">
       <c r="A361">
-        <v>529</v>
+        <v>251</v>
       </c>
       <c r="B361" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C361" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="G361" t="s">
         <v>851</v>
@@ -41706,13 +41712,13 @@
     </row>
     <row r="362" spans="1:9">
       <c r="A362">
-        <v>94</v>
+        <v>529</v>
       </c>
       <c r="B362" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C362" t="s">
-        <v>2180</v>
+        <v>832</v>
       </c>
       <c r="G362" t="s">
         <v>852</v>
@@ -41720,13 +41726,13 @@
     </row>
     <row r="363" spans="1:9">
       <c r="A363">
-        <v>666</v>
+        <v>94</v>
       </c>
       <c r="B363" t="s">
-        <v>2177</v>
+        <v>822</v>
       </c>
       <c r="C363" t="s">
-        <v>834</v>
+        <v>2182</v>
       </c>
       <c r="G363" t="s">
         <v>854</v>
@@ -41734,13 +41740,13 @@
     </row>
     <row r="364" spans="1:9">
       <c r="A364">
-        <v>464</v>
+        <v>666</v>
       </c>
       <c r="B364" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="C364" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G364" t="s">
         <v>856</v>
@@ -41748,13 +41754,13 @@
     </row>
     <row r="365" spans="1:9">
       <c r="A365">
-        <v>659</v>
+        <v>464</v>
       </c>
       <c r="B365" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="C365" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G365" t="s">
         <v>858</v>
@@ -41762,13 +41768,13 @@
     </row>
     <row r="366" spans="1:9">
       <c r="A366">
-        <v>121</v>
+        <v>659</v>
       </c>
       <c r="B366" t="s">
-        <v>826</v>
+        <v>2181</v>
       </c>
       <c r="C366" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G366" t="s">
         <v>860</v>
@@ -41776,13 +41782,13 @@
     </row>
     <row r="367" spans="1:9">
       <c r="A367">
-        <v>376</v>
+        <v>121</v>
       </c>
       <c r="B367" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C367" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G367" t="s">
         <v>862</v>
@@ -41790,13 +41796,13 @@
     </row>
     <row r="368" spans="1:9">
       <c r="A368">
-        <v>102</v>
+        <v>376</v>
       </c>
       <c r="B368" t="s">
-        <v>417</v>
+        <v>827</v>
       </c>
       <c r="C368" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G368" t="s">
         <v>864</v>
@@ -41804,13 +41810,13 @@
     </row>
     <row r="369" spans="1:9">
       <c r="A369">
-        <v>548</v>
+        <v>102</v>
       </c>
       <c r="B369" t="s">
-        <v>830</v>
+        <v>417</v>
       </c>
       <c r="C369" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="G369" t="s">
         <v>866</v>
@@ -41818,13 +41824,13 @@
     </row>
     <row r="370" spans="1:9">
       <c r="A370">
-        <v>461</v>
+        <v>548</v>
       </c>
       <c r="B370" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C370" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G370" t="s">
         <v>868</v>
@@ -41832,13 +41838,13 @@
     </row>
     <row r="371" spans="1:9">
       <c r="A371">
-        <v>104</v>
+        <v>461</v>
       </c>
       <c r="B371" t="s">
-        <v>2180</v>
+        <v>832</v>
       </c>
       <c r="C371" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G371" t="s">
         <v>870</v>
@@ -41846,13 +41852,13 @@
     </row>
     <row r="372" spans="1:9">
       <c r="A372">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="B372" t="s">
-        <v>834</v>
+        <v>2182</v>
       </c>
       <c r="C372" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="G372" t="s">
         <v>578</v>
@@ -41860,13 +41866,13 @@
     </row>
     <row r="373" spans="1:9">
       <c r="A373">
-        <v>565</v>
+        <v>141</v>
       </c>
       <c r="B373" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C373" t="s">
-        <v>1602</v>
+        <v>850</v>
       </c>
       <c r="G373" t="s">
         <v>873</v>
@@ -41874,13 +41880,13 @@
     </row>
     <row r="374" spans="1:9">
       <c r="A374">
-        <v>416</v>
+        <v>565</v>
       </c>
       <c r="B374" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="C374" t="s">
-        <v>438</v>
+        <v>1602</v>
       </c>
       <c r="G374" t="s">
         <v>875</v>
@@ -41888,13 +41894,13 @@
     </row>
     <row r="375" spans="1:9">
       <c r="A375">
-        <v>222</v>
+        <v>416</v>
       </c>
       <c r="B375" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C375" t="s">
-        <v>853</v>
+        <v>438</v>
       </c>
       <c r="G375" t="s">
         <v>877</v>
@@ -41902,13 +41908,13 @@
     </row>
     <row r="376" spans="1:9">
       <c r="A376">
-        <v>662</v>
+        <v>222</v>
       </c>
       <c r="B376" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="C376" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G376" t="s">
         <v>879</v>
@@ -41916,13 +41922,13 @@
     </row>
     <row r="377" spans="1:9">
       <c r="A377">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B377" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="C377" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G377" t="s">
         <v>881</v>
@@ -41930,13 +41936,13 @@
     </row>
     <row r="378" spans="1:9">
       <c r="A378">
-        <v>49</v>
+        <v>660</v>
       </c>
       <c r="B378" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C378" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G378" t="s">
         <v>883</v>
@@ -41944,13 +41950,13 @@
     </row>
     <row r="379" spans="1:9">
       <c r="A379">
-        <v>314</v>
+        <v>49</v>
       </c>
       <c r="B379" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="C379" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G379" t="s">
         <v>886</v>
@@ -41958,13 +41964,13 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380">
-        <v>185</v>
+        <v>314</v>
       </c>
       <c r="B380" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C380" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="G380" t="s">
         <v>888</v>
@@ -41972,13 +41978,13 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B381" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C381" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G381" t="s">
         <v>890</v>
@@ -41986,13 +41992,13 @@
     </row>
     <row r="382" spans="1:9">
       <c r="A382">
-        <v>703</v>
+        <v>167</v>
       </c>
       <c r="B382" t="s">
-        <v>1602</v>
+        <v>850</v>
       </c>
       <c r="C382" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="G382" t="s">
         <v>892</v>
@@ -42000,13 +42006,13 @@
     </row>
     <row r="383" spans="1:9">
       <c r="A383">
-        <v>357</v>
+        <v>703</v>
       </c>
       <c r="B383" t="s">
-        <v>438</v>
+        <v>1602</v>
       </c>
       <c r="C383" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G383" t="s">
         <v>894</v>
@@ -42014,13 +42020,13 @@
     </row>
     <row r="384" spans="1:9">
       <c r="A384">
-        <v>585</v>
+        <v>357</v>
       </c>
       <c r="B384" t="s">
-        <v>853</v>
+        <v>438</v>
       </c>
       <c r="C384" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G384" t="s">
         <v>896</v>
@@ -42028,13 +42034,13 @@
     </row>
     <row r="385" spans="1:9">
       <c r="A385">
-        <v>477</v>
+        <v>585</v>
       </c>
       <c r="B385" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C385" t="s">
-        <v>901</v>
+        <v>871</v>
       </c>
       <c r="G385" t="s">
         <v>898</v>
@@ -42042,13 +42048,13 @@
     </row>
     <row r="386" spans="1:9">
       <c r="A386">
-        <v>550</v>
+        <v>477</v>
       </c>
       <c r="B386" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="C386" t="s">
-        <v>2181</v>
+        <v>901</v>
       </c>
       <c r="G386" t="s">
         <v>900</v>
@@ -42056,13 +42062,13 @@
     </row>
     <row r="387" spans="1:9">
       <c r="A387">
-        <v>521</v>
+        <v>550</v>
       </c>
       <c r="B387" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="C387" t="s">
-        <v>903</v>
+        <v>2183</v>
       </c>
       <c r="G387" t="s">
         <v>902</v>
@@ -42070,13 +42076,13 @@
     </row>
     <row r="388" spans="1:9">
       <c r="A388">
-        <v>146</v>
+        <v>521</v>
       </c>
       <c r="B388" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="C388" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G388" t="s">
         <v>904</v>
@@ -42084,13 +42090,13 @@
     </row>
     <row r="389" spans="1:9">
       <c r="A389">
-        <v>256</v>
+        <v>146</v>
       </c>
       <c r="B389" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C389" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G389" t="s">
         <v>906</v>
@@ -42098,13 +42104,13 @@
     </row>
     <row r="390" spans="1:9">
       <c r="A390">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B390" t="s">
-        <v>884</v>
+        <v>863</v>
       </c>
       <c r="C390" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="G390" t="s">
         <v>908</v>
@@ -42112,13 +42118,13 @@
     </row>
     <row r="391" spans="1:9">
       <c r="A391">
-        <v>643</v>
+        <v>244</v>
       </c>
       <c r="B391" t="s">
-        <v>865</v>
+        <v>884</v>
       </c>
       <c r="C391" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G391" t="s">
         <v>910</v>
@@ -42126,13 +42132,13 @@
     </row>
     <row r="392" spans="1:9">
       <c r="A392">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="B392" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C392" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="G392" t="s">
         <v>912</v>
@@ -42140,13 +42146,13 @@
     </row>
     <row r="393" spans="1:9">
       <c r="A393">
-        <v>175</v>
+        <v>649</v>
       </c>
       <c r="B393" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="C393" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="G393" t="s">
         <v>914</v>
@@ -42154,13 +42160,13 @@
     </row>
     <row r="394" spans="1:9">
       <c r="A394">
-        <v>23</v>
+        <v>175</v>
       </c>
       <c r="B394" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="C394" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G394" t="s">
         <v>916</v>
@@ -42168,13 +42174,13 @@
     </row>
     <row r="395" spans="1:9">
       <c r="A395">
-        <v>312</v>
+        <v>23</v>
       </c>
       <c r="B395" t="s">
-        <v>901</v>
+        <v>871</v>
       </c>
       <c r="C395" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="G395" t="s">
         <v>918</v>
@@ -42182,13 +42188,13 @@
     </row>
     <row r="396" spans="1:9">
       <c r="A396">
-        <v>73</v>
+        <v>312</v>
       </c>
       <c r="B396" t="s">
-        <v>2181</v>
+        <v>901</v>
       </c>
       <c r="C396" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="G396" t="s">
         <v>920</v>
@@ -42196,13 +42202,13 @@
     </row>
     <row r="397" spans="1:9">
       <c r="A397">
-        <v>530</v>
+        <v>73</v>
       </c>
       <c r="B397" t="s">
-        <v>903</v>
+        <v>2183</v>
       </c>
       <c r="C397" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G397" t="s">
         <v>922</v>
@@ -42210,13 +42216,13 @@
     </row>
     <row r="398" spans="1:9">
       <c r="A398">
-        <v>116</v>
+        <v>530</v>
       </c>
       <c r="B398" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="C398" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="G398" t="s">
         <v>580</v>
@@ -42224,13 +42230,13 @@
     </row>
     <row r="399" spans="1:9">
       <c r="A399">
-        <v>202</v>
+        <v>116</v>
       </c>
       <c r="B399" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="C399" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="G399" t="s">
         <v>925</v>
@@ -42238,13 +42244,13 @@
     </row>
     <row r="400" spans="1:9">
       <c r="A400">
-        <v>421</v>
+        <v>202</v>
       </c>
       <c r="B400" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C400" t="s">
-        <v>463</v>
+        <v>927</v>
       </c>
       <c r="G400" t="s">
         <v>199</v>
@@ -42252,13 +42258,13 @@
     </row>
     <row r="401" spans="1:9">
       <c r="A401">
-        <v>605</v>
+        <v>421</v>
       </c>
       <c r="B401" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="C401" t="s">
-        <v>930</v>
+        <v>463</v>
       </c>
       <c r="G401" t="s">
         <v>928</v>
@@ -42266,13 +42272,13 @@
     </row>
     <row r="402" spans="1:9">
       <c r="A402">
-        <v>628</v>
+        <v>605</v>
       </c>
       <c r="B402" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="C402" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="G402" t="s">
         <v>929</v>
@@ -42280,13 +42286,13 @@
     </row>
     <row r="403" spans="1:9">
       <c r="A403">
-        <v>551</v>
+        <v>628</v>
       </c>
       <c r="B403" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="C403" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="G403" t="s">
         <v>931</v>
@@ -42294,13 +42300,13 @@
     </row>
     <row r="404" spans="1:9">
       <c r="A404">
-        <v>238</v>
+        <v>551</v>
       </c>
       <c r="B404" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C404" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="G404" t="s">
         <v>933</v>
@@ -42308,13 +42314,13 @@
     </row>
     <row r="405" spans="1:9">
       <c r="A405">
-        <v>500</v>
+        <v>238</v>
       </c>
       <c r="B405" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
       <c r="C405" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="G405" t="s">
         <v>935</v>
@@ -42322,13 +42328,13 @@
     </row>
     <row r="406" spans="1:9">
       <c r="A406">
-        <v>111</v>
+        <v>500</v>
       </c>
       <c r="B406" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
       <c r="C406" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="G406" t="s">
         <v>937</v>
@@ -42336,13 +42342,13 @@
     </row>
     <row r="407" spans="1:9">
       <c r="A407">
-        <v>645</v>
+        <v>111</v>
       </c>
       <c r="B407" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="C407" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="G407" t="s">
         <v>939</v>
@@ -42350,13 +42356,13 @@
     </row>
     <row r="408" spans="1:9">
       <c r="A408">
-        <v>176</v>
+        <v>645</v>
       </c>
       <c r="B408" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="C408" t="s">
-        <v>471</v>
+        <v>942</v>
       </c>
       <c r="G408" t="s">
         <v>941</v>
@@ -42364,13 +42370,13 @@
     </row>
     <row r="409" spans="1:9">
       <c r="A409">
-        <v>451</v>
+        <v>176</v>
       </c>
       <c r="B409" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C409" t="s">
-        <v>945</v>
+        <v>471</v>
       </c>
       <c r="G409" t="s">
         <v>943</v>
@@ -42378,13 +42384,13 @@
     </row>
     <row r="410" spans="1:9">
       <c r="A410">
-        <v>85</v>
+        <v>451</v>
       </c>
       <c r="B410" t="s">
-        <v>463</v>
+        <v>927</v>
       </c>
       <c r="C410" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="G410" t="s">
         <v>944</v>
@@ -42392,13 +42398,13 @@
     </row>
     <row r="411" spans="1:9">
       <c r="A411">
-        <v>274</v>
+        <v>85</v>
       </c>
       <c r="B411" t="s">
-        <v>947</v>
+        <v>463</v>
       </c>
       <c r="C411" t="s">
-        <v>1790</v>
+        <v>948</v>
       </c>
       <c r="G411" t="s">
         <v>946</v>
@@ -42406,13 +42412,13 @@
     </row>
     <row r="412" spans="1:9">
       <c r="A412">
-        <v>404</v>
+        <v>274</v>
       </c>
       <c r="B412" t="s">
-        <v>930</v>
+        <v>947</v>
       </c>
       <c r="C412" t="s">
-        <v>950</v>
+        <v>1790</v>
       </c>
       <c r="G412" t="s">
         <v>949</v>
@@ -42420,13 +42426,13 @@
     </row>
     <row r="413" spans="1:9">
       <c r="A413">
-        <v>19</v>
+        <v>404</v>
       </c>
       <c r="B413" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="C413" t="s">
-        <v>474</v>
+        <v>950</v>
       </c>
       <c r="G413" t="s">
         <v>211</v>
@@ -42434,13 +42440,13 @@
     </row>
     <row r="414" spans="1:9">
       <c r="A414">
-        <v>547</v>
+        <v>19</v>
       </c>
       <c r="B414" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
       <c r="C414" t="s">
-        <v>952</v>
+        <v>474</v>
       </c>
       <c r="G414" t="s">
         <v>951</v>
@@ -42448,13 +42454,13 @@
     </row>
     <row r="415" spans="1:9">
       <c r="A415">
-        <v>296</v>
+        <v>547</v>
       </c>
       <c r="B415" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="C415" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="G415" t="s">
         <v>953</v>
@@ -42462,13 +42468,13 @@
     </row>
     <row r="416" spans="1:9">
       <c r="A416">
-        <v>41</v>
+        <v>296</v>
       </c>
       <c r="B416" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="C416" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="G416" t="s">
         <v>955</v>
@@ -42476,13 +42482,13 @@
     </row>
     <row r="417" spans="1:9">
       <c r="A417">
-        <v>440</v>
+        <v>41</v>
       </c>
       <c r="B417" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="C417" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="G417" t="s">
         <v>957</v>
@@ -42490,13 +42496,13 @@
     </row>
     <row r="418" spans="1:9">
       <c r="A418">
-        <v>496</v>
+        <v>440</v>
       </c>
       <c r="B418" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="C418" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="G418" t="s">
         <v>959</v>
@@ -42504,13 +42510,13 @@
     </row>
     <row r="419" spans="1:9">
       <c r="A419">
-        <v>139</v>
+        <v>496</v>
       </c>
       <c r="B419" t="s">
-        <v>471</v>
+        <v>942</v>
       </c>
       <c r="C419" t="s">
-        <v>491</v>
+        <v>960</v>
       </c>
       <c r="G419" t="s">
         <v>961</v>
@@ -42518,13 +42524,13 @@
     </row>
     <row r="420" spans="1:9">
       <c r="A420">
-        <v>203</v>
+        <v>139</v>
       </c>
       <c r="B420" t="s">
-        <v>945</v>
+        <v>471</v>
       </c>
       <c r="C420" t="s">
-        <v>963</v>
+        <v>491</v>
       </c>
       <c r="G420" t="s">
         <v>962</v>
@@ -42532,13 +42538,13 @@
     </row>
     <row r="421" spans="1:9">
       <c r="A421">
-        <v>616</v>
+        <v>203</v>
       </c>
       <c r="B421" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="C421" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="G421" t="s">
         <v>964</v>
@@ -42546,13 +42552,13 @@
     </row>
     <row r="422" spans="1:9">
       <c r="A422">
-        <v>686</v>
+        <v>616</v>
       </c>
       <c r="B422" t="s">
-        <v>1790</v>
+        <v>948</v>
       </c>
       <c r="C422" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="G422" t="s">
         <v>966</v>
@@ -42560,13 +42566,13 @@
     </row>
     <row r="423" spans="1:9">
       <c r="A423">
-        <v>131</v>
+        <v>686</v>
       </c>
       <c r="B423" t="s">
-        <v>950</v>
+        <v>1790</v>
       </c>
       <c r="C423" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="G423" t="s">
         <v>968</v>
@@ -42574,13 +42580,13 @@
     </row>
     <row r="424" spans="1:9">
       <c r="A424">
-        <v>371</v>
+        <v>131</v>
       </c>
       <c r="B424" t="s">
-        <v>474</v>
+        <v>950</v>
       </c>
       <c r="C424" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G424" t="s">
         <v>970</v>
@@ -42588,13 +42594,13 @@
     </row>
     <row r="425" spans="1:9">
       <c r="A425">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B425" t="s">
-        <v>952</v>
+        <v>474</v>
       </c>
       <c r="C425" t="s">
-        <v>1905</v>
+        <v>971</v>
       </c>
       <c r="G425" t="s">
         <v>217</v>
@@ -42602,13 +42608,13 @@
     </row>
     <row r="426" spans="1:9">
       <c r="A426">
-        <v>592</v>
+        <v>359</v>
       </c>
       <c r="B426" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C426" t="s">
-        <v>500</v>
+        <v>1903</v>
       </c>
       <c r="G426" t="s">
         <v>973</v>
@@ -42616,13 +42622,13 @@
     </row>
     <row r="427" spans="1:9">
       <c r="A427">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B427" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="C427" t="s">
-        <v>972</v>
+        <v>1905</v>
       </c>
       <c r="G427" t="s">
         <v>583</v>
@@ -42630,13 +42636,13 @@
     </row>
     <row r="428" spans="1:9">
       <c r="A428">
-        <v>544</v>
+        <v>593</v>
       </c>
       <c r="B428" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="C428" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G428" t="s">
         <v>975</v>
@@ -42644,13 +42650,13 @@
     </row>
     <row r="429" spans="1:9">
       <c r="A429">
-        <v>165</v>
+        <v>544</v>
       </c>
       <c r="B429" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="C429" t="s">
-        <v>2182</v>
+        <v>972</v>
       </c>
       <c r="G429" t="s">
         <v>977</v>
@@ -42658,13 +42664,13 @@
     </row>
     <row r="430" spans="1:9">
       <c r="A430">
-        <v>321</v>
+        <v>165</v>
       </c>
       <c r="B430" t="s">
-        <v>491</v>
+        <v>960</v>
       </c>
       <c r="C430" t="s">
-        <v>974</v>
+        <v>503</v>
       </c>
       <c r="G430" t="s">
         <v>220</v>
@@ -42672,13 +42678,13 @@
     </row>
     <row r="431" spans="1:9">
       <c r="A431">
-        <v>377</v>
+        <v>321</v>
       </c>
       <c r="B431" t="s">
-        <v>963</v>
+        <v>491</v>
       </c>
       <c r="C431" t="s">
-        <v>976</v>
+        <v>2184</v>
       </c>
       <c r="G431" t="s">
         <v>980</v>
@@ -42686,13 +42692,13 @@
     </row>
     <row r="432" spans="1:9">
       <c r="A432">
-        <v>469</v>
+        <v>377</v>
       </c>
       <c r="B432" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="C432" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="G432" t="s">
         <v>982</v>
@@ -42700,13 +42706,13 @@
     </row>
     <row r="433" spans="1:9">
       <c r="A433">
-        <v>369</v>
+        <v>469</v>
       </c>
       <c r="B433" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C433" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="G433" t="s">
         <v>984</v>
@@ -42714,13 +42720,13 @@
     </row>
     <row r="434" spans="1:9">
       <c r="A434">
-        <v>536</v>
+        <v>369</v>
       </c>
       <c r="B434" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C434" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="G434" t="s">
         <v>986</v>
@@ -42728,13 +42734,13 @@
     </row>
     <row r="435" spans="1:9">
       <c r="A435">
-        <v>559</v>
+        <v>536</v>
       </c>
       <c r="B435" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="C435" t="s">
-        <v>2183</v>
+        <v>981</v>
       </c>
       <c r="G435" t="s">
         <v>988</v>
@@ -42742,13 +42748,13 @@
     </row>
     <row r="436" spans="1:9">
       <c r="A436">
-        <v>668</v>
+        <v>559</v>
       </c>
       <c r="B436" t="s">
-        <v>1905</v>
+        <v>971</v>
       </c>
       <c r="C436" t="s">
-        <v>2184</v>
+        <v>983</v>
       </c>
       <c r="G436" t="s">
         <v>990</v>
@@ -42756,13 +42762,13 @@
     </row>
     <row r="437" spans="1:9">
       <c r="A437">
-        <v>164</v>
+        <v>721</v>
       </c>
       <c r="B437" t="s">
-        <v>500</v>
+        <v>1903</v>
       </c>
       <c r="C437" t="s">
-        <v>985</v>
+        <v>2185</v>
       </c>
       <c r="G437" t="s">
         <v>992</v>
@@ -42770,13 +42776,13 @@
     </row>
     <row r="438" spans="1:9">
       <c r="A438">
-        <v>519</v>
+        <v>668</v>
       </c>
       <c r="B438" t="s">
-        <v>972</v>
+        <v>1905</v>
       </c>
       <c r="C438" t="s">
-        <v>987</v>
+        <v>2186</v>
       </c>
       <c r="G438" t="s">
         <v>994</v>
@@ -42784,13 +42790,13 @@
     </row>
     <row r="439" spans="1:9">
       <c r="A439">
-        <v>99</v>
+        <v>164</v>
       </c>
       <c r="B439" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C439" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="G439" t="s">
         <v>996</v>
@@ -42798,13 +42804,13 @@
     </row>
     <row r="440" spans="1:9">
       <c r="A440">
-        <v>701</v>
+        <v>519</v>
       </c>
       <c r="B440" t="s">
-        <v>2182</v>
+        <v>972</v>
       </c>
       <c r="C440" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="G440" t="s">
         <v>998</v>
@@ -42812,13 +42818,13 @@
     </row>
     <row r="441" spans="1:9">
       <c r="A441">
-        <v>658</v>
+        <v>99</v>
       </c>
       <c r="B441" t="s">
-        <v>974</v>
+        <v>503</v>
       </c>
       <c r="C441" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="G441" t="s">
         <v>1000</v>
@@ -42826,13 +42832,13 @@
     </row>
     <row r="442" spans="1:9">
       <c r="A442">
-        <v>607</v>
+        <v>701</v>
       </c>
       <c r="B442" t="s">
-        <v>976</v>
+        <v>2184</v>
       </c>
       <c r="C442" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="G442" t="s">
         <v>1002</v>
@@ -42840,13 +42846,13 @@
     </row>
     <row r="443" spans="1:9">
       <c r="A443">
-        <v>34</v>
+        <v>658</v>
       </c>
       <c r="B443" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="C443" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="G443" t="s">
         <v>1004</v>
@@ -42854,13 +42860,13 @@
     </row>
     <row r="444" spans="1:9">
       <c r="A444">
-        <v>159</v>
+        <v>607</v>
       </c>
       <c r="B444" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="C444" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="G444" t="s">
         <v>1006</v>
@@ -42868,13 +42874,13 @@
     </row>
     <row r="445" spans="1:9">
       <c r="A445">
-        <v>240</v>
+        <v>34</v>
       </c>
       <c r="B445" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="C445" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="G445" t="s">
         <v>1008</v>
@@ -42882,13 +42888,13 @@
     </row>
     <row r="446" spans="1:9">
       <c r="A446">
-        <v>107</v>
+        <v>159</v>
       </c>
       <c r="B446" t="s">
-        <v>2183</v>
+        <v>981</v>
       </c>
       <c r="C446" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="G446" t="s">
         <v>1010</v>
@@ -42896,13 +42902,13 @@
     </row>
     <row r="447" spans="1:9">
       <c r="A447">
-        <v>708</v>
+        <v>240</v>
       </c>
       <c r="B447" t="s">
-        <v>2184</v>
+        <v>983</v>
       </c>
       <c r="C447" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="G447" t="s">
         <v>1012</v>
@@ -42910,13 +42916,13 @@
     </row>
     <row r="448" spans="1:9">
       <c r="A448">
-        <v>193</v>
+        <v>107</v>
       </c>
       <c r="B448" t="s">
-        <v>985</v>
+        <v>2185</v>
       </c>
       <c r="C448" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="G448" t="s">
         <v>1014</v>
@@ -42924,13 +42930,13 @@
     </row>
     <row r="449" spans="1:9">
       <c r="A449">
-        <v>615</v>
+        <v>708</v>
       </c>
       <c r="B449" t="s">
-        <v>987</v>
+        <v>2186</v>
       </c>
       <c r="C449" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="G449" t="s">
         <v>1016</v>
@@ -42938,13 +42944,13 @@
     </row>
     <row r="450" spans="1:9">
       <c r="A450">
-        <v>303</v>
+        <v>193</v>
       </c>
       <c r="B450" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="C450" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="G450" t="s">
         <v>1018</v>
@@ -42952,13 +42958,13 @@
     </row>
     <row r="451" spans="1:9">
       <c r="A451">
-        <v>35</v>
+        <v>615</v>
       </c>
       <c r="B451" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="C451" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="G451" t="s">
         <v>1020</v>
@@ -42966,13 +42972,13 @@
     </row>
     <row r="452" spans="1:9">
       <c r="A452">
-        <v>637</v>
+        <v>303</v>
       </c>
       <c r="B452" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="C452" t="s">
-        <v>2185</v>
+        <v>1011</v>
       </c>
       <c r="G452" t="s">
         <v>1022</v>
@@ -42980,13 +42986,13 @@
     </row>
     <row r="453" spans="1:9">
       <c r="A453">
-        <v>631</v>
+        <v>35</v>
       </c>
       <c r="B453" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="C453" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="G453" t="s">
         <v>1023</v>
@@ -42994,13 +43000,13 @@
     </row>
     <row r="454" spans="1:9">
       <c r="A454">
-        <v>383</v>
+        <v>637</v>
       </c>
       <c r="B454" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="C454" t="s">
-        <v>1019</v>
+        <v>2187</v>
       </c>
       <c r="G454" t="s">
         <v>1025</v>
@@ -43008,13 +43014,13 @@
     </row>
     <row r="455" spans="1:9">
       <c r="A455">
-        <v>245</v>
+        <v>631</v>
       </c>
       <c r="B455" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="C455" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="G455" t="s">
         <v>1027</v>
@@ -43022,13 +43028,13 @@
     </row>
     <row r="456" spans="1:9">
       <c r="A456">
-        <v>442</v>
+        <v>383</v>
       </c>
       <c r="B456" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="C456" t="s">
-        <v>524</v>
+        <v>1019</v>
       </c>
       <c r="G456" t="s">
         <v>1029</v>
@@ -43036,13 +43042,13 @@
     </row>
     <row r="457" spans="1:9">
       <c r="A457">
-        <v>36</v>
+        <v>245</v>
       </c>
       <c r="B457" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="C457" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="G457" t="s">
         <v>1031</v>
@@ -43050,13 +43056,13 @@
     </row>
     <row r="458" spans="1:9">
       <c r="A458">
-        <v>37</v>
+        <v>442</v>
       </c>
       <c r="B458" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="C458" t="s">
-        <v>2186</v>
+        <v>524</v>
       </c>
       <c r="G458" t="s">
         <v>43</v>
@@ -43064,13 +43070,13 @@
     </row>
     <row r="459" spans="1:9">
       <c r="A459">
-        <v>599</v>
+        <v>36</v>
       </c>
       <c r="B459" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="C459" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="G459" t="s">
         <v>1034</v>
@@ -43078,13 +43084,13 @@
     </row>
     <row r="460" spans="1:9">
       <c r="A460">
-        <v>606</v>
+        <v>37</v>
       </c>
       <c r="B460" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="C460" t="s">
-        <v>1036</v>
+        <v>2188</v>
       </c>
       <c r="G460" t="s">
         <v>224</v>
@@ -43092,13 +43098,13 @@
     </row>
     <row r="461" spans="1:9">
       <c r="A461">
-        <v>199</v>
+        <v>599</v>
       </c>
       <c r="B461" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="C461" t="s">
-        <v>2187</v>
+        <v>1028</v>
       </c>
       <c r="G461" t="s">
         <v>1037</v>
@@ -43106,13 +43112,13 @@
     </row>
     <row r="462" spans="1:9">
       <c r="A462">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="B462" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="C462" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="G462" t="s">
         <v>1039</v>
@@ -43120,13 +43126,13 @@
     </row>
     <row r="463" spans="1:9">
       <c r="A463">
-        <v>280</v>
+        <v>199</v>
       </c>
       <c r="B463" t="s">
-        <v>2185</v>
+        <v>1011</v>
       </c>
       <c r="C463" t="s">
-        <v>1042</v>
+        <v>2189</v>
       </c>
       <c r="G463" t="s">
         <v>1041</v>
@@ -43134,13 +43140,13 @@
     </row>
     <row r="464" spans="1:9">
       <c r="A464">
-        <v>38</v>
+        <v>617</v>
       </c>
       <c r="B464" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C464" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="G464" t="s">
         <v>1043</v>
@@ -43148,13 +43154,13 @@
     </row>
     <row r="465" spans="1:9">
       <c r="A465">
-        <v>319</v>
+        <v>280</v>
       </c>
       <c r="B465" t="s">
-        <v>1019</v>
+        <v>2187</v>
       </c>
       <c r="C465" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="G465" t="s">
         <v>1045</v>
@@ -43162,13 +43168,13 @@
     </row>
     <row r="466" spans="1:9">
       <c r="A466">
-        <v>317</v>
+        <v>38</v>
       </c>
       <c r="B466" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="C466" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="G466" t="s">
         <v>591</v>
@@ -43176,13 +43182,13 @@
     </row>
     <row r="467" spans="1:9">
       <c r="A467">
-        <v>168</v>
+        <v>319</v>
       </c>
       <c r="B467" t="s">
-        <v>524</v>
+        <v>1019</v>
       </c>
       <c r="C467" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="G467" t="s">
         <v>1048</v>
@@ -43190,13 +43196,13 @@
     </row>
     <row r="468" spans="1:9">
       <c r="A468">
-        <v>581</v>
+        <v>317</v>
       </c>
       <c r="B468" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="C468" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="G468" t="s">
         <v>1050</v>
@@ -43204,13 +43210,13 @@
     </row>
     <row r="469" spans="1:9">
       <c r="A469">
-        <v>692</v>
+        <v>168</v>
       </c>
       <c r="B469" t="s">
-        <v>2186</v>
+        <v>524</v>
       </c>
       <c r="C469" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="G469" t="s">
         <v>1052</v>
@@ -43218,13 +43224,13 @@
     </row>
     <row r="470" spans="1:9">
       <c r="A470">
-        <v>401</v>
+        <v>581</v>
       </c>
       <c r="B470" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="C470" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="G470" t="s">
         <v>1054</v>
@@ -43232,13 +43238,13 @@
     </row>
     <row r="471" spans="1:9">
       <c r="A471">
-        <v>541</v>
+        <v>692</v>
       </c>
       <c r="B471" t="s">
-        <v>1036</v>
+        <v>2188</v>
       </c>
       <c r="C471" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="G471" t="s">
         <v>593</v>
@@ -43246,13 +43252,13 @@
     </row>
     <row r="472" spans="1:9">
       <c r="A472">
-        <v>355</v>
+        <v>401</v>
       </c>
       <c r="B472" t="s">
-        <v>2187</v>
+        <v>1028</v>
       </c>
       <c r="C472" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="G472" t="s">
         <v>1057</v>
@@ -43260,13 +43266,13 @@
     </row>
     <row r="473" spans="1:9">
       <c r="A473">
-        <v>55</v>
+        <v>541</v>
       </c>
       <c r="B473" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="C473" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="G473" t="s">
         <v>1059</v>
@@ -43274,13 +43280,13 @@
     </row>
     <row r="474" spans="1:9">
       <c r="A474">
-        <v>297</v>
+        <v>355</v>
       </c>
       <c r="B474" t="s">
-        <v>1042</v>
+        <v>2189</v>
       </c>
       <c r="C474" t="s">
-        <v>2188</v>
+        <v>1060</v>
       </c>
       <c r="G474" t="s">
         <v>1061</v>
@@ -43288,13 +43294,13 @@
     </row>
     <row r="475" spans="1:9">
       <c r="A475">
-        <v>396</v>
+        <v>55</v>
       </c>
       <c r="B475" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="C475" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="G475" t="s">
         <v>1063</v>
@@ -43302,13 +43308,13 @@
     </row>
     <row r="476" spans="1:9">
       <c r="A476">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B476" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="C476" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="G476" t="s">
         <v>1065</v>
@@ -43316,13 +43322,13 @@
     </row>
     <row r="477" spans="1:9">
       <c r="A477">
-        <v>197</v>
+        <v>396</v>
       </c>
       <c r="B477" t="s">
-        <v>1047</v>
+        <v>1044</v>
       </c>
       <c r="C477" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="G477" t="s">
         <v>1067</v>
@@ -43330,13 +43336,13 @@
     </row>
     <row r="478" spans="1:9">
       <c r="A478">
-        <v>40</v>
+        <v>288</v>
       </c>
       <c r="B478" t="s">
-        <v>1049</v>
+        <v>1046</v>
       </c>
       <c r="C478" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="G478" t="s">
         <v>597</v>
@@ -43344,13 +43350,13 @@
     </row>
     <row r="479" spans="1:9">
       <c r="A479">
-        <v>400</v>
+        <v>197</v>
       </c>
       <c r="B479" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="C479" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="G479" t="s">
         <v>1070</v>
@@ -43358,13 +43364,13 @@
     </row>
     <row r="480" spans="1:9">
       <c r="A480">
-        <v>375</v>
+        <v>40</v>
       </c>
       <c r="B480" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="C480" t="s">
-        <v>1071</v>
+        <v>2192</v>
       </c>
       <c r="G480" t="s">
         <v>1072</v>
@@ -43372,13 +43378,13 @@
     </row>
     <row r="481" spans="1:9">
       <c r="A481">
-        <v>230</v>
+        <v>400</v>
       </c>
       <c r="B481" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="C481" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="G481" t="s">
         <v>1074</v>
@@ -43386,13 +43392,13 @@
     </row>
     <row r="482" spans="1:9">
       <c r="A482">
-        <v>573</v>
+        <v>375</v>
       </c>
       <c r="B482" t="s">
-        <v>1056</v>
+        <v>1053</v>
       </c>
       <c r="C482" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="G482" t="s">
         <v>1076</v>
@@ -43400,13 +43406,13 @@
     </row>
     <row r="483" spans="1:9">
       <c r="A483">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="B483" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="C483" t="s">
-        <v>2191</v>
+        <v>1073</v>
       </c>
       <c r="G483" t="s">
         <v>1078</v>
@@ -43414,13 +43420,13 @@
     </row>
     <row r="484" spans="1:9">
       <c r="A484">
-        <v>630</v>
+        <v>573</v>
       </c>
       <c r="B484" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="C484" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="G484" t="s">
         <v>1080</v>
@@ -43428,13 +43434,13 @@
     </row>
     <row r="485" spans="1:9">
       <c r="A485">
-        <v>653</v>
+        <v>163</v>
       </c>
       <c r="B485" t="s">
-        <v>2188</v>
+        <v>1060</v>
       </c>
       <c r="C485" t="s">
-        <v>1079</v>
+        <v>2193</v>
       </c>
       <c r="G485" t="s">
         <v>1082</v>
@@ -43442,13 +43448,13 @@
     </row>
     <row r="486" spans="1:9">
       <c r="A486">
-        <v>534</v>
+        <v>630</v>
       </c>
       <c r="B486" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="C486" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="G486" t="s">
         <v>1084</v>
@@ -43456,13 +43462,13 @@
     </row>
     <row r="487" spans="1:9">
       <c r="A487">
-        <v>687</v>
+        <v>653</v>
       </c>
       <c r="B487" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="C487" t="s">
-        <v>1086</v>
+        <v>1079</v>
       </c>
       <c r="G487" t="s">
         <v>1085</v>
@@ -43470,13 +43476,13 @@
     </row>
     <row r="488" spans="1:9">
       <c r="A488">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="B488" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="C488" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="G488" t="s">
         <v>1087</v>
@@ -43484,13 +43490,13 @@
     </row>
     <row r="489" spans="1:9">
       <c r="A489">
-        <v>671</v>
+        <v>687</v>
       </c>
       <c r="B489" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="C489" t="s">
-        <v>560</v>
+        <v>1086</v>
       </c>
       <c r="G489" t="s">
         <v>1089</v>
@@ -43498,13 +43504,13 @@
     </row>
     <row r="490" spans="1:9">
       <c r="A490">
-        <v>311</v>
+        <v>520</v>
       </c>
       <c r="B490" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="C490" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="G490" t="s">
         <v>1090</v>
@@ -43512,13 +43518,13 @@
     </row>
     <row r="491" spans="1:9">
       <c r="A491">
-        <v>517</v>
+        <v>671</v>
       </c>
       <c r="B491" t="s">
-        <v>1071</v>
+        <v>2192</v>
       </c>
       <c r="C491" t="s">
-        <v>1093</v>
+        <v>560</v>
       </c>
       <c r="G491" t="s">
         <v>1092</v>
@@ -43526,13 +43532,13 @@
     </row>
     <row r="492" spans="1:9">
       <c r="A492">
-        <v>281</v>
+        <v>311</v>
       </c>
       <c r="B492" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="C492" t="s">
-        <v>13</v>
+        <v>1091</v>
       </c>
       <c r="G492" t="s">
         <v>1094</v>
@@ -43540,13 +43546,13 @@
     </row>
     <row r="493" spans="1:9">
       <c r="A493">
-        <v>260</v>
+        <v>517</v>
       </c>
       <c r="B493" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="C493" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="G493" t="s">
         <v>1095</v>
@@ -43554,13 +43560,13 @@
     </row>
     <row r="494" spans="1:9">
       <c r="A494">
-        <v>674</v>
+        <v>281</v>
       </c>
       <c r="B494" t="s">
-        <v>2191</v>
+        <v>1073</v>
       </c>
       <c r="C494" t="s">
-        <v>565</v>
+        <v>13</v>
       </c>
       <c r="G494" t="s">
         <v>242</v>
@@ -43568,13 +43574,13 @@
     </row>
     <row r="495" spans="1:9">
       <c r="A495">
-        <v>512</v>
+        <v>260</v>
       </c>
       <c r="B495" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="C495" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G495" t="s">
         <v>1097</v>
@@ -43582,13 +43588,13 @@
     </row>
     <row r="496" spans="1:9">
       <c r="A496">
-        <v>669</v>
+        <v>674</v>
       </c>
       <c r="B496" t="s">
-        <v>1079</v>
+        <v>2193</v>
       </c>
       <c r="C496" t="s">
-        <v>1100</v>
+        <v>565</v>
       </c>
       <c r="G496" t="s">
         <v>1099</v>
@@ -43596,10 +43602,13 @@
     </row>
     <row r="497" spans="1:9">
       <c r="A497">
-        <v>284</v>
+        <v>512</v>
       </c>
       <c r="B497" t="s">
-        <v>1081</v>
+        <v>1077</v>
+      </c>
+      <c r="C497" t="s">
+        <v>1098</v>
       </c>
       <c r="G497" t="s">
         <v>1101</v>
@@ -43607,10 +43616,13 @@
     </row>
     <row r="498" spans="1:9">
       <c r="A498">
-        <v>610</v>
+        <v>669</v>
       </c>
       <c r="B498" t="s">
-        <v>1086</v>
+        <v>1079</v>
+      </c>
+      <c r="C498" t="s">
+        <v>1100</v>
       </c>
       <c r="G498" t="s">
         <v>1102</v>
@@ -43618,10 +43630,10 @@
     </row>
     <row r="499" spans="1:9">
       <c r="A499">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="B499" t="s">
-        <v>1088</v>
+        <v>1081</v>
       </c>
       <c r="G499" t="s">
         <v>1103</v>
@@ -43629,10 +43641,10 @@
     </row>
     <row r="500" spans="1:9">
       <c r="A500">
-        <v>363</v>
+        <v>610</v>
       </c>
       <c r="B500" t="s">
-        <v>560</v>
+        <v>1086</v>
       </c>
       <c r="G500" t="s">
         <v>1104</v>
@@ -43640,10 +43652,10 @@
     </row>
     <row r="501" spans="1:9">
       <c r="A501">
-        <v>570</v>
+        <v>313</v>
       </c>
       <c r="B501" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="G501" t="s">
         <v>1105</v>
@@ -43651,10 +43663,10 @@
     </row>
     <row r="502" spans="1:9">
       <c r="A502">
-        <v>234</v>
+        <v>363</v>
       </c>
       <c r="B502" t="s">
-        <v>1093</v>
+        <v>560</v>
       </c>
       <c r="G502" t="s">
         <v>1106</v>
@@ -43662,10 +43674,10 @@
     </row>
     <row r="503" spans="1:9">
       <c r="A503">
-        <v>503</v>
+        <v>570</v>
       </c>
       <c r="B503" t="s">
-        <v>13</v>
+        <v>1091</v>
       </c>
       <c r="G503" t="s">
         <v>1107</v>
@@ -43673,10 +43685,10 @@
     </row>
     <row r="504" spans="1:9">
       <c r="A504">
-        <v>198</v>
+        <v>234</v>
       </c>
       <c r="B504" t="s">
-        <v>1096</v>
+        <v>1093</v>
       </c>
       <c r="G504" t="s">
         <v>1108</v>
@@ -43684,10 +43696,10 @@
     </row>
     <row r="505" spans="1:9">
       <c r="A505">
-        <v>397</v>
+        <v>503</v>
       </c>
       <c r="B505" t="s">
-        <v>565</v>
+        <v>13</v>
       </c>
       <c r="G505" t="s">
         <v>1109</v>
@@ -43695,10 +43707,10 @@
     </row>
     <row r="506" spans="1:9">
       <c r="A506">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="B506" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="G506" t="s">
         <v>1110</v>
@@ -43706,21 +43718,33 @@
     </row>
     <row r="507" spans="1:9">
       <c r="A507">
-        <v>379</v>
+        <v>397</v>
       </c>
       <c r="B507" t="s">
-        <v>1100</v>
+        <v>565</v>
       </c>
       <c r="G507" t="s">
         <v>1111</v>
       </c>
     </row>
     <row r="508" spans="1:9">
+      <c r="A508">
+        <v>136</v>
+      </c>
+      <c r="B508" t="s">
+        <v>1098</v>
+      </c>
       <c r="G508" t="s">
         <v>1112</v>
       </c>
     </row>
     <row r="509" spans="1:9">
+      <c r="A509">
+        <v>379</v>
+      </c>
+      <c r="B509" t="s">
+        <v>1100</v>
+      </c>
       <c r="G509" t="s">
         <v>1113</v>
       </c>
@@ -44487,7 +44511,7 @@
     </row>
     <row r="662" spans="1:9">
       <c r="G662" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="663" spans="1:9">
@@ -45272,7 +45296,7 @@
     </row>
     <row r="819" spans="1:9">
       <c r="G819" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
     </row>
     <row r="820" spans="1:9">
@@ -46842,7 +46866,7 @@
     </row>
     <row r="1133" spans="1:9">
       <c r="G1133" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="1134" spans="1:9">
